--- a/sources/michelle_step8.xlsx
+++ b/sources/michelle_step8.xlsx
@@ -908,11 +908,6 @@
           <t>d</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
       <c r="Z7" t="inlineStr">
         <is>
           <t>f1c6a2cd-8f86-45e2-8020-1482f8fb6c52</t>

--- a/sources/michelle_step8.xlsx
+++ b/sources/michelle_step8.xlsx
@@ -7332,12 +7332,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Launching Shuttle [~5]</t>
+          <t>Launching Shuttle</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Launching Shuttle [~5]</t>
+          <t>Launching Shuttle</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">

--- a/sources/michelle_step8.xlsx
+++ b/sources/michelle_step8.xlsx
@@ -856,6 +856,11 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>151f3bbe-77de-4044-9738-f8670c4da698</t>
+        </is>
+      </c>
       <c r="Z6" t="inlineStr">
         <is>
           <t>151f3bbe-77de-4044-9738-f8670c4da698</t>
@@ -908,6 +913,11 @@
           <t>d</t>
         </is>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>f1c6a2cd-8f86-45e2-8020-1482f8fb6c52</t>
+        </is>
+      </c>
       <c r="Z7" t="inlineStr">
         <is>
           <t>f1c6a2cd-8f86-45e2-8020-1482f8fb6c52</t>
@@ -975,6 +985,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>b56b385d-5cb6-4b61-a390-be7a9104c9cf</t>
+        </is>
+      </c>
       <c r="Z8" t="inlineStr">
         <is>
           <t>b56b385d-5cb6-4b61-a390-be7a9104c9cf</t>
@@ -1037,6 +1052,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>736d0fd3-1148-4734-be27-34a2a82b7048</t>
+        </is>
+      </c>
       <c r="Z9" t="inlineStr">
         <is>
           <t>736d0fd3-1148-4734-be27-34a2a82b7048</t>
@@ -1097,6 +1117,11 @@
       <c r="U10" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>e0cf556a-57d8-4762-b577-f4d445bc558f</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -9080,6 +9105,11 @@
           <t>hmmhLmhhLm</t>
         </is>
       </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>0fc0ca0b-d962-4684-9515-834d1e1283b6</t>
+        </is>
+      </c>
       <c r="Z100" t="inlineStr">
         <is>
           <t>0fc0ca0b-d962-4684-9515-834d1e1283b6</t>
@@ -9127,6 +9157,11 @@
           <t>hmmhLmmLm!</t>
         </is>
       </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>b5de5a0d-851a-4ca2-ad04-246afb578ddb</t>
+        </is>
+      </c>
       <c r="Z101" t="inlineStr">
         <is>
           <t>b5de5a0d-851a-4ca2-ad04-246afb578ddb</t>
@@ -9172,6 +9207,11 @@
       <c r="S102" t="inlineStr">
         <is>
           <t>hmmhLmmmLm</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>04575a0d-bb87-4254-a98a-681589f81afc</t>
         </is>
       </c>
       <c r="Z102" t="inlineStr">

--- a/sources/michelle_step8.xlsx
+++ b/sources/michelle_step8.xlsx
@@ -417,37 +417,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB102"/>
+  <dimension ref="A1:AC102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col hidden="1" min="4" max="4"/>
-    <col width="46" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col hidden="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col hidden="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
-    <col hidden="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col hidden="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col hidden="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col hidden="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col hidden="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col hidden="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col hidden="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
-    <col hidden="1" min="16" max="16"/>
-    <col width="22" customWidth="1" min="17" max="17"/>
-    <col hidden="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="103" customWidth="1" min="23" max="23"/>
-    <col width="10" customWidth="1" min="24" max="24"/>
-    <col width="38" customWidth="1" min="25" max="25"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col hidden="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col hidden="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="103" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="25" max="25"/>
     <col width="38" customWidth="1" min="26" max="26"/>
     <col width="38" customWidth="1" min="27" max="27"/>
-    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="38" customWidth="1" min="28" max="28"/>
+    <col width="11" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -475,125 +476,130 @@
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="N2" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
+      <c r="O2" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="P2" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="P2" s="1" t="inlineStr">
+      <c r="Q2" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="Q2" s="1" t="inlineStr">
+      <c r="R2" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="R2" s="1" t="inlineStr">
+      <c r="S2" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="S2" s="1" t="inlineStr">
+      <c r="T2" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="T2" s="1" t="inlineStr">
+      <c r="U2" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="U2" s="1" t="inlineStr">
+      <c r="V2" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="V2" s="1" t="inlineStr">
+      <c r="W2" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="W2" s="1" t="inlineStr">
+      <c r="X2" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="X2" s="1" t="inlineStr">
+      <c r="Y2" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Y2" s="1" t="inlineStr">
+      <c r="Z2" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Z2" s="1" t="inlineStr">
+      <c r="AA2" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AA2" s="1" t="inlineStr">
+      <c r="AB2" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AB2" s="1" t="inlineStr">
+      <c r="AC2" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -610,57 +616,57 @@
           <t>1+3</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Front Suplex</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Front Suplex</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>ae80d2db-e2fc-41f9-8c23-7326b805e167</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>1bae1de1-8a01-4d10-bd58-bfaa71268bf2</t>
         </is>
@@ -677,57 +683,57 @@
           <t>2+4</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Fisherman Suplex</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Fisherman Suplex</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>4be20815-9ccb-4b87-b2ab-563ca3a7d91f</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>7f1dcb2c-f5a4-4f5f-990a-6a4aac441405</t>
         </is>
@@ -744,57 +750,57 @@
           <t>df+1+2</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Arm Lock Suplex</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Arm Lock Suplex</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>f0f97379-3a80-47e1-b56a-e9bb3d43ff64</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>6a7fc30d-aea9-45be-a681-d9b653aaa48b</t>
         </is>
@@ -811,62 +817,62 @@
           <t>b+2</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Arm Whip</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Arm Whip</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>d</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>Special Tag Throw with Julia only. Julia finishes with a Running Bulldog. Total damage is 12,24.</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>151f3bbe-77de-4044-9738-f8670c4da698</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>151f3bbe-77de-4044-9738-f8670c4da698</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -883,52 +889,52 @@
           <t>b+2,d+1+2</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>– Rear Suplex</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Arm Whip – Rear Suplex</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>12,45</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>d</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>f1c6a2cd-8f86-45e2-8020-1482f8fb6c52</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>f1c6a2cd-8f86-45e2-8020-1482f8fb6c52</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>151f3bbe-77de-4044-9738-f8670c4da698</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -952,50 +958,55 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>Blizard Suplex</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Blizard Suplex</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Left</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>b56b385d-5cb6-4b61-a390-be7a9104c9cf</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>b56b385d-5cb6-4b61-a390-be7a9104c9cf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1019,50 +1030,55 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>Southern Cross Suplex</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Southern Cross Suplex</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Right</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>736d0fd3-1148-4734-be27-34a2a82b7048</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>736d0fd3-1148-4734-be27-34a2a82b7048</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1086,50 +1102,55 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>Rear Suplex</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Rear Suplex</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Back</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>e0cf556a-57d8-4762-b577-f4d445bc558f</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>e0cf556a-57d8-4762-b577-f4d445bc558f</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1161,125 +1182,130 @@
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="E13" s="1" t="inlineStr">
+      <c r="F13" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="F13" s="1" t="inlineStr">
+      <c r="G13" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="G13" s="1" t="inlineStr">
+      <c r="H13" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="H13" s="1" t="inlineStr">
+      <c r="I13" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="I13" s="1" t="inlineStr">
+      <c r="J13" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="J13" s="1" t="inlineStr">
+      <c r="K13" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="K13" s="1" t="inlineStr">
+      <c r="L13" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="L13" s="1" t="inlineStr">
+      <c r="M13" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="M13" s="1" t="inlineStr">
+      <c r="N13" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="N13" s="1" t="inlineStr">
+      <c r="O13" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="O13" s="1" t="inlineStr">
+      <c r="P13" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="P13" s="1" t="inlineStr">
+      <c r="Q13" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="Q13" s="1" t="inlineStr">
+      <c r="R13" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="R13" s="1" t="inlineStr">
+      <c r="S13" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="S13" s="1" t="inlineStr">
+      <c r="T13" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="T13" s="1" t="inlineStr">
+      <c r="U13" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="U13" s="1" t="inlineStr">
+      <c r="V13" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="V13" s="1" t="inlineStr">
+      <c r="W13" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="W13" s="1" t="inlineStr">
+      <c r="X13" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="X13" s="1" t="inlineStr">
+      <c r="Y13" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Y13" s="1" t="inlineStr">
+      <c r="Z13" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Z13" s="1" t="inlineStr">
+      <c r="AA13" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AA13" s="1" t="inlineStr">
+      <c r="AB13" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AB13" s="1" t="inlineStr">
+      <c r="AC13" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -1296,77 +1322,77 @@
           <t>1</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>c6033170-fc6f-41ba-a03a-01b8aaf76e68</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>07ce9c8f-23a9-4d57-8e2e-0b53aa195908</t>
         </is>
@@ -1383,77 +1409,77 @@
           <t>2</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>7ee48452-ecf0-4e47-9e91-025d60848d80</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>68e8fa5c-b7a2-4e20-a74b-c7513611726f</t>
         </is>
@@ -1470,77 +1496,77 @@
           <t>3</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>a5606039-9ce1-4b7f-b85d-f6400494d9ff</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>72c31814-4f1f-4b4a-895d-98ee23de95ee</t>
         </is>
@@ -1557,77 +1583,77 @@
           <t>4</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>686545e2-829e-443e-b4c8-9afb1ab22fd1</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>323db6b0-f3e0-4fac-aa55-636e0ff56b9d</t>
         </is>
@@ -1644,77 +1670,77 @@
           <t>f+1</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>003ea89d-245e-4ecf-a870-27b43aa73f51</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>06c2823e-acfb-4422-9092-e8a5b2433449</t>
         </is>
@@ -1731,77 +1757,77 @@
           <t>f+2</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>cbd0f936-ebdc-4a00-9b7d-ee77f15c1c41</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>9f424d4e-45d3-4e2b-a510-2bce905bcee1</t>
         </is>
@@ -1818,77 +1844,77 @@
           <t>f+3</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>f7d4503e-eb69-4def-bf82-52ad23e0146d</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>98afa8e3-4411-4663-bc7d-078228b3d1d8</t>
         </is>
@@ -1905,77 +1931,77 @@
           <t>f+4</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>24275688-5897-45e5-9139-9315f9df4062</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>ac220679-3490-4372-a7fb-7a57d3cb2ef4</t>
         </is>
@@ -1992,77 +2018,77 @@
           <t>d+1</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>7f5a2e81-ff5d-40c2-ba9e-f962140e37cb</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>ff9207d7-f21a-43c0-b432-e8e0378ea769</t>
         </is>
@@ -2079,77 +2105,77 @@
           <t>d+2</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>f20c1a12-e493-4f99-ab06-70b120c75788</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>b0b03e78-02c3-4108-aa77-3af9ba1c9cdb</t>
         </is>
@@ -2166,77 +2192,77 @@
           <t>d+3</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>8fa2057e-0c2d-4012-94a8-1fb2fedc94cc</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>0ff15731-ad31-4a6e-8b0e-6c2f6be90646</t>
         </is>
@@ -2253,77 +2279,77 @@
           <t>d+4</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>d3470262-1904-4531-adf4-5a81a970055d</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>c181cbde-fea4-4334-a79f-506ad4c2ee7e</t>
         </is>
@@ -2340,77 +2366,77 @@
           <t>FC+1</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>f885b616-b303-4b52-b32d-972fd7e4b968</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>fa9aa0bc-4a3b-436e-96b4-b66c616dd1d2</t>
         </is>
@@ -2427,77 +2453,77 @@
           <t>FC+2</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>7064dd06-e117-4818-8886-1da7e10b0239</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>72664919-c993-4044-ae65-0679e9da2480</t>
         </is>
@@ -2514,77 +2540,77 @@
           <t>FC+3</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>437979bc-f7aa-4448-8a71-5c942fd40369</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
+      <c r="AA28" t="inlineStr">
         <is>
           <t>6d9f53d2-b02a-4008-9e3c-b2ade8c87e14</t>
         </is>
@@ -2601,77 +2627,77 @@
           <t>FC+4</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>63d37d7e-80e3-4840-ba9c-0051bba960ff</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>ce93e07c-a3ea-4497-b3d1-942aeba96d92</t>
         </is>
@@ -2688,77 +2714,77 @@
           <t>WS+1</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>45ce8ef0-85b9-4e4e-b2b9-3bcb73441a6a</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>22ce4c72-e30f-40fe-8d67-b3801ad23f3e</t>
         </is>
@@ -2775,77 +2801,77 @@
           <t>WS+2</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>-11</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>-11</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>76267b4b-2763-4391-97bf-83dd2c0520dd</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>46487fe7-bf44-4cad-b534-afe79efc0b70</t>
         </is>
@@ -2862,77 +2888,77 @@
           <t>WS+3</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>3706c6b1-0fa1-4a1f-9f88-a60645b682d0</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>24e073de-e439-4048-af3f-df400b03385b</t>
         </is>
@@ -2949,77 +2975,77 @@
           <t>WS+4</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>a4a15337-a47f-4860-aa35-c4bde965e01b</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>fe59a187-8ce3-4127-80c9-5546a390b4c3</t>
         </is>
@@ -3036,77 +3062,77 @@
           <t>df+1</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>85e20006-05ae-4532-a1a8-647332d09cac</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>05dfb79f-79f9-4e09-8ada-db0ce4fb168c</t>
         </is>
@@ -3123,77 +3149,77 @@
           <t>df+2</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>42dc9699-91a5-4f0f-87ac-980938243165</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
+      <c r="AA35" t="inlineStr">
         <is>
           <t>03456ef2-ec89-46af-ba68-eaf6a8c163a4</t>
         </is>
@@ -3210,77 +3236,77 @@
           <t>df+3</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="R36" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y36" t="inlineStr">
+      <c r="Z36" t="inlineStr">
         <is>
           <t>483fec58-19b9-4705-aa78-4dd3faa96ec5</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>fe00be93-e80a-4b6c-b722-119c842f22ea</t>
         </is>
@@ -3297,77 +3323,77 @@
           <t>df+4</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="R37" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y37" t="inlineStr">
+      <c r="Z37" t="inlineStr">
         <is>
           <t>834b467d-4bf0-475e-8c25-701077632fbe</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
+      <c r="AA37" t="inlineStr">
         <is>
           <t>6de38d6f-c7c6-4e62-9eb4-e57135f82b61</t>
         </is>
@@ -3399,125 +3425,130 @@
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="E40" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="E40" s="1" t="inlineStr">
+      <c r="F40" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="F40" s="1" t="inlineStr">
+      <c r="G40" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="G40" s="1" t="inlineStr">
+      <c r="H40" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="H40" s="1" t="inlineStr">
+      <c r="I40" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="I40" s="1" t="inlineStr">
+      <c r="J40" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="J40" s="1" t="inlineStr">
+      <c r="K40" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="K40" s="1" t="inlineStr">
+      <c r="L40" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="L40" s="1" t="inlineStr">
+      <c r="M40" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="M40" s="1" t="inlineStr">
+      <c r="N40" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="N40" s="1" t="inlineStr">
+      <c r="O40" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="O40" s="1" t="inlineStr">
+      <c r="P40" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="P40" s="1" t="inlineStr">
+      <c r="Q40" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="Q40" s="1" t="inlineStr">
+      <c r="R40" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="R40" s="1" t="inlineStr">
+      <c r="S40" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="S40" s="1" t="inlineStr">
+      <c r="T40" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="T40" s="1" t="inlineStr">
+      <c r="U40" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="U40" s="1" t="inlineStr">
+      <c r="V40" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="V40" s="1" t="inlineStr">
+      <c r="W40" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="W40" s="1" t="inlineStr">
+      <c r="X40" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="X40" s="1" t="inlineStr">
+      <c r="Y40" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Y40" s="1" t="inlineStr">
+      <c r="Z40" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Z40" s="1" t="inlineStr">
+      <c r="AA40" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AA40" s="1" t="inlineStr">
+      <c r="AB40" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AB40" s="1" t="inlineStr">
+      <c r="AC40" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -3534,92 +3565,92 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Twin Arrow</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>Twin Arrow</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="R41" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
+      <c r="W41" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="Y41" t="inlineStr">
+      <c r="Z41" t="inlineStr">
         <is>
           <t>4482f91b-86b4-4a8f-a816-db2b2f2fbd46</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
+      <c r="AA41" t="inlineStr">
         <is>
           <t>e9b6c796-c000-4ed2-8368-c690971c3c01</t>
         </is>
@@ -3636,97 +3667,97 @@
           <t>f+1</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>Flash Uppercut</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Flash Uppercut</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="R42" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="S42" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="T42" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="W42" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
+      <c r="Y42" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr">
+      <c r="Z42" t="inlineStr">
         <is>
           <t>7bfbcd5b-ddbe-4aa7-b650-8564323234ed</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
+      <c r="AA42" t="inlineStr">
         <is>
           <t>77114bb1-2d92-497f-a701-65b23a7a3dc3</t>
         </is>
@@ -3743,87 +3774,87 @@
           <t>d,df+1</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>Flash Punch</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>Flash Punch</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="R43" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y43" t="inlineStr">
+      <c r="Z43" t="inlineStr">
         <is>
           <t>06464f67-c803-4f17-b171-2197c0239e6f</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
+      <c r="AA43" t="inlineStr">
         <is>
           <t>b7444905-de92-415b-b2fe-4a95a0cf40ea</t>
         </is>
@@ -3840,92 +3871,92 @@
           <t>1~1</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>G-Clef - Club Fist</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>G-Clef - Club Fist</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>0 -15</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>0 -15</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>+6 -4</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>+6 -4</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>+6 -4</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>+6 -4</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>10,5</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="R44" t="inlineStr">
         <is>
           <t>10,5</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>hm</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>hm</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>Damage of the 1st punch is only 5 if the 2nd punch isn't executed.</t>
         </is>
       </c>
-      <c r="Y44" t="inlineStr">
+      <c r="Z44" t="inlineStr">
         <is>
           <t>ab733431-ae0b-47eb-b429-70ddf9a50561</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
+      <c r="AA44" t="inlineStr">
         <is>
           <t>319b3d6e-6130-4f50-9ab9-93ca205ab84e</t>
         </is>
@@ -3942,97 +3973,97 @@
           <t>1~1,1</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>– Flash Uppercut</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>G-Clef - Club Fist – Flash Uppercut</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>0 -15 -14</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>+6 -4 KD</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>+6 -4 KD</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="R45" t="inlineStr">
         <is>
           <t>10,5,21</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>hmm</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
+      <c r="W45" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
+      <c r="Y45" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Y45" t="inlineStr">
+      <c r="Z45" t="inlineStr">
         <is>
           <t>d8373306-9820-4552-b536-0bed8b49a0a3</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
+      <c r="AA45" t="inlineStr">
         <is>
           <t>b2044aba-d99f-4d1d-aa13-7d104d07f1bb</t>
         </is>
       </c>
-      <c r="AA45" t="inlineStr">
+      <c r="AB45" t="inlineStr">
         <is>
           <t>ab733431-ae0b-47eb-b429-70ddf9a50561</t>
         </is>
@@ -4049,87 +4080,87 @@
           <t>1~1,4,3</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>– Bow &amp; Arrow</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>G-Clef - Club Fist – Bow &amp; Arrow</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>-13 -12</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>0 -15 -13 -12</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>-2 KD</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>+6 -4 -2 KD</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>-2 KD</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>+6 -4 -2 KD</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>12,15</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="R46" t="inlineStr">
         <is>
           <t>10,5,12,15</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>Lm</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>hmLm</t>
         </is>
       </c>
-      <c r="Y46" t="inlineStr">
+      <c r="Z46" t="inlineStr">
         <is>
           <t>db045429-faae-403f-9a70-90085ac5800d</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
+      <c r="AA46" t="inlineStr">
         <is>
           <t>a8c95e80-af11-47a1-b203-bea91b893aa3</t>
         </is>
       </c>
-      <c r="AA46" t="inlineStr">
+      <c r="AB46" t="inlineStr">
         <is>
           <t>ab733431-ae0b-47eb-b429-70ddf9a50561</t>
         </is>
@@ -4146,87 +4177,87 @@
           <t>df+1</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>Club Fist</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Club Fist</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="R47" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y47" t="inlineStr">
+      <c r="Z47" t="inlineStr">
         <is>
           <t>6f5042e4-8e92-4267-8d5e-9039bd5ffdbe</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
+      <c r="AA47" t="inlineStr">
         <is>
           <t>45e928fe-2dae-464b-b94d-bf1038f0acb5</t>
         </is>
@@ -4243,97 +4274,97 @@
           <t>df+1,1</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>– Flash Uppercut</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Club Fist – Flash Uppercut</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>-15 -14</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>-4 KD</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>-4 KD</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="R48" t="inlineStr">
         <is>
           <t>8,21</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr">
+      <c r="W48" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
+      <c r="Y48" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Y48" t="inlineStr">
+      <c r="Z48" t="inlineStr">
         <is>
           <t>937031b4-16d7-4706-9af8-7c3cc587432e</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
+      <c r="AA48" t="inlineStr">
         <is>
           <t>969ae53c-460d-46a5-b67e-34c8fe3c2f4e</t>
         </is>
       </c>
-      <c r="AA48" t="inlineStr">
+      <c r="AB48" t="inlineStr">
         <is>
           <t>6f5042e4-8e92-4267-8d5e-9039bd5ffdbe</t>
         </is>
@@ -4350,87 +4381,87 @@
           <t>df+1,4,3</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>– Bow &amp; Arrow</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>Club Fist – Bow &amp; Arrow</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>-13 -12</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>-15 -13 -12</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>-2 KD</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>-4 -2 KD</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>-2 KD</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>-4 -2 KD</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>12,15</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="R49" t="inlineStr">
         <is>
           <t>8,12,15</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
+      <c r="S49" t="inlineStr">
         <is>
           <t>Lm</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="T49" t="inlineStr">
         <is>
           <t>mLm</t>
         </is>
       </c>
-      <c r="Y49" t="inlineStr">
+      <c r="Z49" t="inlineStr">
         <is>
           <t>5799327f-0f65-4b2d-a011-7a75a92eefcf</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
+      <c r="AA49" t="inlineStr">
         <is>
           <t>b1bc079d-23df-4712-a7c6-aad9b7fea595</t>
         </is>
       </c>
-      <c r="AA49" t="inlineStr">
+      <c r="AB49" t="inlineStr">
         <is>
           <t>6f5042e4-8e92-4267-8d5e-9039bd5ffdbe</t>
         </is>
@@ -4447,92 +4478,92 @@
           <t>1~2</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>G-Clef - Gut Punch</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>G-Clef - Gut Punch</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>0 -15</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>0 -15</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>+6 +5</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>+6 +5</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>+6 +5</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>+6 +5</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>5,8</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="R50" t="inlineStr">
         <is>
           <t>5,8</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="S50" t="inlineStr">
         <is>
           <t>hm</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>hm</t>
         </is>
       </c>
-      <c r="W50" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>Damage of the 1st punch is only 5 if the 2nd punch isn't executed.</t>
         </is>
       </c>
-      <c r="Y50" t="inlineStr">
+      <c r="Z50" t="inlineStr">
         <is>
           <t>6f3db68f-f7e3-4d29-aa20-fddf7ac8ab21</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
+      <c r="AA50" t="inlineStr">
         <is>
           <t>93869afa-9cfe-4d58-ac4e-9f08aa9a710d</t>
         </is>
@@ -4549,87 +4580,87 @@
           <t>1~2~1</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>– Skyscraper Cannon</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>G-Clef - Gut Punch – Skyscraper Cannon</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>0 -15</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>+6 +5</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>+6 +5</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="R51" t="inlineStr">
         <is>
           <t>5,8,21</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t>hmm</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr">
+      <c r="W51" t="inlineStr">
         <is>
           <t>CH</t>
         </is>
       </c>
-      <c r="W51" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>The 3rd only occurs if the 1st hit was a counter hit. Second hit will be 15 damage.</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
+      <c r="Y51" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Y51" t="inlineStr">
+      <c r="Z51" t="inlineStr">
         <is>
           <t>f0f2bfda-dfa5-40f3-ae66-b166200ab547</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
+      <c r="AA51" t="inlineStr">
         <is>
           <t>5748a150-d4fb-48bb-a663-98ec4b5a96ed</t>
         </is>
       </c>
-      <c r="AA51" t="inlineStr">
+      <c r="AB51" t="inlineStr">
         <is>
           <t>6f3db68f-f7e3-4d29-aa20-fddf7ac8ab21</t>
         </is>
@@ -4646,92 +4677,92 @@
           <t>1~2,3</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>– Low Kick</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>G-Clef - Gut Punch – Low Kick</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>0 -15 -17</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>+6 +5 -3</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>+6 +5 -3</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="P52" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="Q52" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="R52" t="inlineStr">
         <is>
           <t>5,8,10</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="T52" t="inlineStr">
         <is>
           <t>hmL</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr">
+      <c r="W52" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Y52" t="inlineStr">
+      <c r="Z52" t="inlineStr">
         <is>
           <t>eea0f2f5-415d-4625-b39b-23047f52db49</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
+      <c r="AA52" t="inlineStr">
         <is>
           <t>3c8fe17b-396a-488a-a85f-f6d1acec196d</t>
         </is>
       </c>
-      <c r="AA52" t="inlineStr">
+      <c r="AB52" t="inlineStr">
         <is>
           <t>6f3db68f-f7e3-4d29-aa20-fddf7ac8ab21</t>
         </is>
@@ -4748,87 +4779,87 @@
           <t>1~2,4</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>– High Kick</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>G-Clef - Gut Punch – High Kick</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>0 -15 -7</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>+6 +5 -7</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>+6 +5 KD</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="R53" t="inlineStr">
         <is>
           <t>5,8,20</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="T53" t="inlineStr">
         <is>
           <t>hmh</t>
         </is>
       </c>
-      <c r="Y53" t="inlineStr">
+      <c r="Z53" t="inlineStr">
         <is>
           <t>5e4f379b-fd36-4665-83c6-0a7d14eaeba8</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
+      <c r="AA53" t="inlineStr">
         <is>
           <t>e175c8a1-2fcf-4f30-ae5e-0c4b8bcc5292</t>
         </is>
       </c>
-      <c r="AA53" t="inlineStr">
+      <c r="AB53" t="inlineStr">
         <is>
           <t>6f3db68f-f7e3-4d29-aa20-fddf7ac8ab21</t>
         </is>
@@ -4845,67 +4876,67 @@
           <t>f,f+1</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>Party Crasher</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>Party Crasher</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="R54" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="T54" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y54" t="inlineStr">
+      <c r="Z54" t="inlineStr">
         <is>
           <t>23604313-0807-4e0f-a7dd-2c0696a15708</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
+      <c r="AA54" t="inlineStr">
         <is>
           <t>617ebe68-c949-400b-81d8-85f59e446512</t>
         </is>
@@ -4922,92 +4953,92 @@
           <t>f,f+1,4</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>– Skyscraper Kick</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>Party Crasher – Skyscraper Kick</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>-11</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>-2 -11</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="R55" t="inlineStr">
         <is>
           <t>10,15</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="T55" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr">
+      <c r="W55" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Y55" t="inlineStr">
+      <c r="Z55" t="inlineStr">
         <is>
           <t>ac6252ff-738b-45cf-8214-59a0c37c6bb9</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
+      <c r="AA55" t="inlineStr">
         <is>
           <t>843b60ee-5df5-4ab3-84db-e8eeafa986f1</t>
         </is>
       </c>
-      <c r="AA55" t="inlineStr">
+      <c r="AB55" t="inlineStr">
         <is>
           <t>23604313-0807-4e0f-a7dd-2c0696a15708</t>
         </is>
@@ -5024,87 +5055,87 @@
           <t>SS+1</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>Pusher</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>Pusher</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="R56" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="T56" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y56" t="inlineStr">
+      <c r="Z56" t="inlineStr">
         <is>
           <t>fc206d44-cab0-4658-a3ea-a475200d4790</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
+      <c r="AA56" t="inlineStr">
         <is>
           <t>de1ebccf-5ffe-4cc0-91c2-e18e22c1748a</t>
         </is>
@@ -5121,87 +5152,87 @@
           <t>1+4,3</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>Club Fist - Bow &amp; Arrow</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>Club Fist - Bow &amp; Arrow</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>20 x x</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>20 x x</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>x -13 -12</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>x -13 -12</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>x -2 KD</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>x -2 KD</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>x -2 KD</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>x -2 KD</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>12,12,15</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="R57" t="inlineStr">
         <is>
           <t>12,12,15</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>mLm</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
+      <c r="T57" t="inlineStr">
         <is>
           <t>mLm</t>
         </is>
       </c>
-      <c r="Y57" t="inlineStr">
+      <c r="Z57" t="inlineStr">
         <is>
           <t>f8532bb5-92b1-4c79-ace5-f60ecd8ba147</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
+      <c r="AA57" t="inlineStr">
         <is>
           <t>e0af4fa2-4df5-418b-8873-74301385876f</t>
         </is>
@@ -5218,87 +5249,87 @@
           <t>df+2</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>Gut Punch</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>Gut Punch</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="Q58" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="R58" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr">
+      <c r="S58" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
+      <c r="T58" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y58" t="inlineStr">
+      <c r="Z58" t="inlineStr">
         <is>
           <t>660febf4-407c-4515-8a00-893c6e865407</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
+      <c r="AA58" t="inlineStr">
         <is>
           <t>be76ff29-47a8-439b-8fb9-996d53c57fba</t>
         </is>
@@ -5315,87 +5346,87 @@
           <t>df+2,1</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>– Skyscraper Cannon</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>Gut Punch – Skyscraper Cannon</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="Q59" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="R59" t="inlineStr">
         <is>
           <t>10,21</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr">
+      <c r="S59" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="T59" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr">
+      <c r="W59" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="W59" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>In the d/f+2,1 string the damage of the d/f+2 is 15. And has to hit from the front to work.</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
+      <c r="Y59" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Y59" t="inlineStr">
+      <c r="Z59" t="inlineStr">
         <is>
           <t>f6d1c15e-318b-4d1b-aa4a-cdda0a81c936</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
+      <c r="AA59" t="inlineStr">
         <is>
           <t>9b9cf09b-7031-473b-8cc5-2134ac0c7650</t>
         </is>
       </c>
-      <c r="AA59" t="inlineStr">
+      <c r="AB59" t="inlineStr">
         <is>
           <t>660febf4-407c-4515-8a00-893c6e865407</t>
         </is>
@@ -5412,92 +5443,92 @@
           <t>df+2,3</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>– Low Kick</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>Gut Punch – Low Kick</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>-6 -17</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>+5 -3</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>+5 -3</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="R60" t="inlineStr">
         <is>
           <t>10,10</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr">
+      <c r="S60" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
+      <c r="T60" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="V60" t="inlineStr">
+      <c r="W60" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Y60" t="inlineStr">
+      <c r="Z60" t="inlineStr">
         <is>
           <t>2d24d3a4-3fbf-489e-946b-372cd70d2695</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
+      <c r="AA60" t="inlineStr">
         <is>
           <t>addf3734-8445-428d-a7e3-f8992a5672c7</t>
         </is>
       </c>
-      <c r="AA60" t="inlineStr">
+      <c r="AB60" t="inlineStr">
         <is>
           <t>660febf4-407c-4515-8a00-893c6e865407</t>
         </is>
@@ -5514,87 +5545,87 @@
           <t>df+2,4</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>– High Kick</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>Gut Punch – High Kick</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>-6 -7</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>+5 -7</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>+5 -7</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="P61" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="Q61" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="R61" t="inlineStr">
         <is>
           <t>10,20</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr">
+      <c r="S61" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="T61" t="inlineStr">
         <is>
           <t>mh</t>
         </is>
       </c>
-      <c r="Y61" t="inlineStr">
+      <c r="Z61" t="inlineStr">
         <is>
           <t>26065c0d-b052-4723-bbc4-cd6e91cac2ea</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
+      <c r="AA61" t="inlineStr">
         <is>
           <t>90f0c93e-2635-4dd7-85de-7c9e7235db55</t>
         </is>
       </c>
-      <c r="AA61" t="inlineStr">
+      <c r="AB61" t="inlineStr">
         <is>
           <t>660febf4-407c-4515-8a00-893c6e865407</t>
         </is>
@@ -5618,95 +5649,100 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t>2+3,1</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
           <t>Ultimate Cannon</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>Ultimate Cannon</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>10 x x</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>10 x x</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>x -11 -8</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>x -11 -8</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>x 0 KD</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>x 0 KD</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t>x 0 KD</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>x 0 KD</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>(9,10_8,9) ,25</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t>(9,10_8,9) ,25</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="R62" t="inlineStr">
         <is>
           <t>(9,10_8,9) ,25</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr">
+      <c r="S62" t="inlineStr">
         <is>
           <t>Smm</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
+      <c r="T62" t="inlineStr">
         <is>
           <t>Smm</t>
         </is>
       </c>
-      <c r="V62" t="inlineStr">
+      <c r="W62" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
+      <c r="Y62" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Y62" t="inlineStr">
+      <c r="Z62" t="inlineStr">
         <is>
           <t>8a215398-0f57-4a39-9571-610535427a9a</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
+      <c r="AA62" t="inlineStr">
         <is>
           <t>c6169995-1ea9-4ac8-b0f4-ad1d786a2576</t>
         </is>
@@ -5723,87 +5759,87 @@
           <t>f,f+2</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>Hunter</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>Hunter</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>-19</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>-19</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="R63" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr">
+      <c r="S63" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
+      <c r="T63" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y63" t="inlineStr">
+      <c r="Z63" t="inlineStr">
         <is>
           <t>a808579c-0674-4bdb-b65f-9096ce4b6758</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
+      <c r="AA63" t="inlineStr">
         <is>
           <t>c1dd9a34-d556-4a34-ac56-15bd884a77c0</t>
         </is>
@@ -5820,92 +5856,92 @@
           <t>FC+df+2</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>Flash Elbow</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>Flash Elbow</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>-19</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>-19</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr">
+      <c r="R64" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr">
+      <c r="S64" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
+      <c r="T64" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V64" t="inlineStr">
+      <c r="W64" t="inlineStr">
         <is>
           <t>FSc</t>
         </is>
       </c>
-      <c r="Y64" t="inlineStr">
+      <c r="Z64" t="inlineStr">
         <is>
           <t>87f85a0a-7f51-44f3-b998-581d928eeba1</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
+      <c r="AA64" t="inlineStr">
         <is>
           <t>ce656918-6b00-4c70-8e77-af065888dd3c</t>
         </is>
@@ -5922,92 +5958,92 @@
           <t>d,DF+2</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>Flash Arrow</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>Flash Arrow</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="Q65" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="R65" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr">
+      <c r="S65" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
+      <c r="T65" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V65" t="inlineStr">
+      <c r="W65" t="inlineStr">
         <is>
           <t>FSc</t>
         </is>
       </c>
-      <c r="Y65" t="inlineStr">
+      <c r="Z65" t="inlineStr">
         <is>
           <t>edc9a051-b046-434a-835f-9467782d9d59</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
+      <c r="AA65" t="inlineStr">
         <is>
           <t>8d37e67b-149f-4d33-b868-666825292756</t>
         </is>
@@ -6024,92 +6060,92 @@
           <t>SS+2</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>Snake Step</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>Snake Step</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t>+11</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>+11</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>+11</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>+11</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
+      <c r="P66" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="Q66" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr">
+      <c r="R66" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr">
+      <c r="S66" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
+      <c r="T66" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="V66" t="inlineStr">
+      <c r="W66" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Y66" t="inlineStr">
+      <c r="Z66" t="inlineStr">
         <is>
           <t>2a148049-2090-4522-839b-231b42e377b2</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
+      <c r="AA66" t="inlineStr">
         <is>
           <t>9d2e08d7-7a85-4416-bea2-6deee558f452</t>
         </is>
@@ -6126,87 +6162,87 @@
           <t>SS+2~1</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>Inner Palm Crush</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>Inner Palm Crush</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
+      <c r="O67" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr">
+      <c r="P67" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr">
+      <c r="Q67" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr">
+      <c r="R67" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R67" t="inlineStr">
+      <c r="S67" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
+      <c r="T67" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y67" t="inlineStr">
+      <c r="Z67" t="inlineStr">
         <is>
           <t>38a980c2-e824-4483-a085-22f60e0f1f94</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
+      <c r="AA67" t="inlineStr">
         <is>
           <t>40324b95-4f78-4bde-bc38-fc6694dbce1f</t>
         </is>
@@ -6230,95 +6266,100 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t>2~b</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
           <t>Arm Whip</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>Arm Whip</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
+      <c r="O68" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr">
+      <c r="P68" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="Q68" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr">
+      <c r="R68" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr">
+      <c r="S68" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
+      <c r="T68" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="V68" t="inlineStr">
+      <c r="W68" t="inlineStr">
         <is>
           <t>OB</t>
         </is>
       </c>
-      <c r="W68" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>The Arm Whip needs to hit for Michelle to spin around the opponent.</t>
         </is>
       </c>
-      <c r="Y68" t="inlineStr">
+      <c r="Z68" t="inlineStr">
         <is>
           <t>65aaecf4-ea4f-4d97-b0ed-4df6be392720</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
+      <c r="AA68" t="inlineStr">
         <is>
           <t>658a2394-ca26-4994-a95e-31cfe4fd82b7</t>
         </is>
@@ -6335,92 +6376,92 @@
           <t>b+2,1+2</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>– Back Push</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>Arm Whip – Back Push</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t>-2 +2</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t>-1 +2</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr">
+      <c r="O69" t="inlineStr">
         <is>
           <t>-1 +2</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr">
+      <c r="P69" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr">
+      <c r="Q69" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr">
+      <c r="R69" t="inlineStr">
         <is>
           <t>12,-</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr">
+      <c r="S69" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr">
+      <c r="T69" t="inlineStr">
         <is>
           <t>h-</t>
         </is>
       </c>
-      <c r="W69" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>Causes Special Tag Throw with Julia, see the Grappling Arts.</t>
         </is>
       </c>
-      <c r="Y69" t="inlineStr">
+      <c r="Z69" t="inlineStr">
         <is>
           <t>8045d9f7-3789-4f1b-b9c6-3335bf7f87f4</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
+      <c r="AA69" t="inlineStr">
         <is>
           <t>3c2c5a63-03b4-44d5-ab93-663e488b4621</t>
         </is>
       </c>
-      <c r="AA69" t="inlineStr">
+      <c r="AB69" t="inlineStr">
         <is>
           <t>65aaecf4-ea4f-4d97-b0ed-4df6be392720</t>
         </is>
@@ -6444,85 +6485,90 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t>3~2</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
           <t>Tequila Sunrise</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>Tequila Sunrise</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>-11</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t>-11</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="N70" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
+      <c r="O70" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr">
+      <c r="P70" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr">
+      <c r="Q70" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr">
+      <c r="R70" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr">
+      <c r="S70" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
+      <c r="T70" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y70" t="inlineStr">
+      <c r="Z70" t="inlineStr">
         <is>
           <t>bee9bf66-30d0-4443-bef6-34689f2aa7a4</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
+      <c r="AA70" t="inlineStr">
         <is>
           <t>e81a796c-f340-41b5-a698-f27760fff81a</t>
         </is>
@@ -6539,92 +6585,92 @@
           <t>WS+2,2</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>– Flash Elbow</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>Tequila Sunrise – Flash Elbow</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t>-20</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t>-11 -20</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t>0 KD</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="N71" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr">
+      <c r="O71" t="inlineStr">
         <is>
           <t>0 KD</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr">
+      <c r="P71" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
+      <c r="Q71" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr">
+      <c r="R71" t="inlineStr">
         <is>
           <t>15,21</t>
         </is>
       </c>
-      <c r="R71" t="inlineStr">
+      <c r="S71" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
+      <c r="T71" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="V71" t="inlineStr">
+      <c r="W71" t="inlineStr">
         <is>
           <t>FSc</t>
         </is>
       </c>
-      <c r="Y71" t="inlineStr">
+      <c r="Z71" t="inlineStr">
         <is>
           <t>2181b545-43c1-4ea4-8383-a1261da73f46</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
+      <c r="AA71" t="inlineStr">
         <is>
           <t>40f18677-b60d-4782-80f3-070d61fbc19c</t>
         </is>
       </c>
-      <c r="AA71" t="inlineStr">
+      <c r="AB71" t="inlineStr">
         <is>
           <t>bee9bf66-30d0-4443-bef6-34689f2aa7a4</t>
         </is>
@@ -6641,102 +6687,102 @@
           <t>WS+2,1,1</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>– Club Fist - Flash Uppercut</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>Tequila Sunrise – Club Fist - Flash Uppercut</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t>-15 -14</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t>-11 -15 -14</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t>-4 KD</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t>0 -4 KD</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
+      <c r="N72" t="inlineStr">
         <is>
           <t>-4 KD</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr">
+      <c r="O72" t="inlineStr">
         <is>
           <t>0 -4 KD</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr">
+      <c r="P72" t="inlineStr">
         <is>
           <t>5,21</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr">
+      <c r="Q72" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr">
+      <c r="R72" t="inlineStr">
         <is>
           <t>15,5,21</t>
         </is>
       </c>
-      <c r="R72" t="inlineStr">
+      <c r="S72" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
+      <c r="T72" t="inlineStr">
         <is>
           <t>mmm</t>
         </is>
       </c>
-      <c r="V72" t="inlineStr">
+      <c r="W72" t="inlineStr">
         <is>
           <t>SH</t>
         </is>
       </c>
-      <c r="W72" t="inlineStr">
+      <c r="X72" t="inlineStr">
         <is>
           <t>The uppercut does not juggle, but you can buffer in a tag. The WS+2 will be 18 damage in this string.</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr">
+      <c r="Y72" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Y72" t="inlineStr">
+      <c r="Z72" t="inlineStr">
         <is>
           <t>b3d79555-32d1-4f7a-a46f-fceb5629b5e5</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
+      <c r="AA72" t="inlineStr">
         <is>
           <t>8b8200eb-982a-44c5-8e29-d260aebe4a31</t>
         </is>
       </c>
-      <c r="AA72" t="inlineStr">
+      <c r="AB72" t="inlineStr">
         <is>
           <t>bee9bf66-30d0-4443-bef6-34689f2aa7a4</t>
         </is>
@@ -6753,87 +6799,87 @@
           <t>WS+2,1,4,3</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>– Club Fist - Bow &amp; Arrow</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>Tequila Sunrise – Club Fist - Bow &amp; Arrow</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>-15 -13 -12</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t>-11 -15 -13 -12</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t>-4 -2 KD</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t>0 -4 -2 KD</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
+      <c r="N73" t="inlineStr">
         <is>
           <t>-4 -2 KD</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr">
+      <c r="O73" t="inlineStr">
         <is>
           <t>0 -4 -2 KD</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr">
+      <c r="P73" t="inlineStr">
         <is>
           <t>5,12,15</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr">
+      <c r="Q73" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr">
+      <c r="R73" t="inlineStr">
         <is>
           <t>15,5,12,15</t>
         </is>
       </c>
-      <c r="R73" t="inlineStr">
+      <c r="S73" t="inlineStr">
         <is>
           <t>mLm</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr">
+      <c r="T73" t="inlineStr">
         <is>
           <t>mmLm</t>
         </is>
       </c>
-      <c r="Y73" t="inlineStr">
+      <c r="Z73" t="inlineStr">
         <is>
           <t>71b47a62-1587-4e81-8847-61cc025f0a65</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
+      <c r="AA73" t="inlineStr">
         <is>
           <t>f97f6dc6-5fac-430c-a556-502a73658de8</t>
         </is>
       </c>
-      <c r="AA73" t="inlineStr">
+      <c r="AB73" t="inlineStr">
         <is>
           <t>bee9bf66-30d0-4443-bef6-34689f2aa7a4</t>
         </is>
@@ -6850,92 +6896,92 @@
           <t>WS+2,4</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>– Razor Sweep</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>Tequila Sunrise – Razor Sweep</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="K74" t="inlineStr">
         <is>
           <t>-11 -10</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t>0 +1</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
+      <c r="N74" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr">
+      <c r="O74" t="inlineStr">
         <is>
           <t>0 +1</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr">
+      <c r="P74" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr">
+      <c r="Q74" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr">
+      <c r="R74" t="inlineStr">
         <is>
           <t>15,12</t>
         </is>
       </c>
-      <c r="R74" t="inlineStr">
+      <c r="S74" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="S74" t="inlineStr">
+      <c r="T74" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="V74" t="inlineStr">
+      <c r="W74" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Y74" t="inlineStr">
+      <c r="Z74" t="inlineStr">
         <is>
           <t>8c47d298-512c-4637-8a95-f4eefeab55db</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
+      <c r="AA74" t="inlineStr">
         <is>
           <t>64178fd6-bc5d-4dc7-8aa6-1dc89b6f5cc7</t>
         </is>
       </c>
-      <c r="AA74" t="inlineStr">
+      <c r="AB74" t="inlineStr">
         <is>
           <t>bee9bf66-30d0-4443-bef6-34689f2aa7a4</t>
         </is>
@@ -6952,87 +6998,87 @@
           <t>WS+2,4,4</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>–– High Kick</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>Tequila Sunrise – Razor Sweep – High Kick</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t>-19</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t>-11 -10 -19</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t>0 +1 -3</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="N75" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
+      <c r="O75" t="inlineStr">
         <is>
           <t>0 +1 -3</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr">
+      <c r="P75" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr">
+      <c r="Q75" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr">
+      <c r="R75" t="inlineStr">
         <is>
           <t>15,12,23</t>
         </is>
       </c>
-      <c r="R75" t="inlineStr">
+      <c r="S75" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr">
+      <c r="T75" t="inlineStr">
         <is>
           <t>mLh</t>
         </is>
       </c>
-      <c r="Y75" t="inlineStr">
+      <c r="Z75" t="inlineStr">
         <is>
           <t>94cac373-fba9-44cc-9a61-2fb0ea840049</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
+      <c r="AA75" t="inlineStr">
         <is>
           <t>5c834826-130d-4b25-9d07-710095bdba42</t>
         </is>
       </c>
-      <c r="AA75" t="inlineStr">
+      <c r="AB75" t="inlineStr">
         <is>
           <t>8c47d298-512c-4637-8a95-f4eefeab55db</t>
         </is>
@@ -7049,92 +7095,92 @@
           <t>WS+2,4,d+4</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>–– Low Kick</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>Tequila Sunrise – Razor Sweep – Low Kick</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t>-11 -10 -14</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t>0 +1 -8</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
+      <c r="N76" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr">
+      <c r="O76" t="inlineStr">
         <is>
           <t>0 +1 -8</t>
         </is>
       </c>
-      <c r="O76" t="inlineStr">
+      <c r="P76" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr">
+      <c r="Q76" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr">
+      <c r="R76" t="inlineStr">
         <is>
           <t>15,12,10</t>
         </is>
       </c>
-      <c r="R76" t="inlineStr">
+      <c r="S76" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr">
+      <c r="T76" t="inlineStr">
         <is>
           <t>mLL</t>
         </is>
       </c>
-      <c r="V76" t="inlineStr">
+      <c r="W76" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Y76" t="inlineStr">
+      <c r="Z76" t="inlineStr">
         <is>
           <t>e642aecd-da2d-4165-8a88-d5169cf2cba1</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
+      <c r="AA76" t="inlineStr">
         <is>
           <t>387e027b-fae4-4785-b2f8-0289299c1f13</t>
         </is>
       </c>
-      <c r="AA76" t="inlineStr">
+      <c r="AB76" t="inlineStr">
         <is>
           <t>8c47d298-512c-4637-8a95-f4eefeab55db</t>
         </is>
@@ -7151,92 +7197,92 @@
           <t>WS+2,4,1</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>–– Razor's Edge</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>Tequila Sunrise – Razor Sweep – Razor's Edge</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t>-18</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="K77" t="inlineStr">
         <is>
           <t>-11 -10 -18</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t>0 +1 KD</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr">
+      <c r="N77" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr">
+      <c r="O77" t="inlineStr">
         <is>
           <t>0 +1 KD</t>
         </is>
       </c>
-      <c r="O77" t="inlineStr">
+      <c r="P77" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr">
+      <c r="Q77" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="Q77" t="inlineStr">
+      <c r="R77" t="inlineStr">
         <is>
           <t>15,12,21</t>
         </is>
       </c>
-      <c r="R77" t="inlineStr">
+      <c r="S77" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr">
+      <c r="T77" t="inlineStr">
         <is>
           <t>mLm</t>
         </is>
       </c>
-      <c r="V77" t="inlineStr">
+      <c r="W77" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Y77" t="inlineStr">
+      <c r="Z77" t="inlineStr">
         <is>
           <t>96fccc74-6da2-4336-9b80-13f17ce2633d</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
+      <c r="AA77" t="inlineStr">
         <is>
           <t>4717213d-d345-480f-8ca9-28bad35cebbc</t>
         </is>
       </c>
-      <c r="AA77" t="inlineStr">
+      <c r="AB77" t="inlineStr">
         <is>
           <t>8c47d298-512c-4637-8a95-f4eefeab55db</t>
         </is>
@@ -7253,92 +7299,92 @@
           <t>SS+3~4</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>Scissor Cut</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>Scissor Cut</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t>-11 -10</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="K78" t="inlineStr">
         <is>
           <t>-11 -10</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t>0 KD</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t>0 KD</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr">
+      <c r="N78" t="inlineStr">
         <is>
           <t>0 KD</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr">
+      <c r="O78" t="inlineStr">
         <is>
           <t>0 KD</t>
         </is>
       </c>
-      <c r="O78" t="inlineStr">
+      <c r="P78" t="inlineStr">
         <is>
           <t>16,18</t>
         </is>
       </c>
-      <c r="P78" t="inlineStr">
+      <c r="Q78" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="Q78" t="inlineStr">
+      <c r="R78" t="inlineStr">
         <is>
           <t>16,18</t>
         </is>
       </c>
-      <c r="R78" t="inlineStr">
+      <c r="S78" t="inlineStr">
         <is>
           <t>mh</t>
         </is>
       </c>
-      <c r="S78" t="inlineStr">
+      <c r="T78" t="inlineStr">
         <is>
           <t>mh</t>
         </is>
       </c>
-      <c r="V78" t="inlineStr">
+      <c r="W78" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Y78" t="inlineStr">
+      <c r="Z78" t="inlineStr">
         <is>
           <t>4ecf8681-97c9-4403-af9e-2fb09d5ab440</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
+      <c r="AA78" t="inlineStr">
         <is>
           <t>4d6108e5-d72a-46bd-98be-5787e189d614</t>
         </is>
@@ -7355,102 +7401,102 @@
           <t>df+3+4</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>Launching Shuttle</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>Launching Shuttle</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>24 x</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>24 x</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t>x -8</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t>x -8</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t>x KD</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t>x KD</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr">
+      <c r="N79" t="inlineStr">
         <is>
           <t>x KD</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr">
+      <c r="O79" t="inlineStr">
         <is>
           <t>x KD</t>
         </is>
       </c>
-      <c r="O79" t="inlineStr">
+      <c r="P79" t="inlineStr">
         <is>
           <t>14,21</t>
         </is>
       </c>
-      <c r="P79" t="inlineStr">
+      <c r="Q79" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="Q79" t="inlineStr">
+      <c r="R79" t="inlineStr">
         <is>
           <t>14,21</t>
         </is>
       </c>
-      <c r="R79" t="inlineStr">
+      <c r="S79" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr">
+      <c r="T79" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="V79" t="inlineStr">
+      <c r="W79" t="inlineStr">
         <is>
           <t>JG GB</t>
         </is>
       </c>
-      <c r="W79" t="inlineStr">
+      <c r="X79" t="inlineStr">
         <is>
           <t>When blocked low the Launching Shuttle will cause List Stun.</t>
         </is>
       </c>
-      <c r="X79" t="inlineStr">
+      <c r="Y79" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Y79" t="inlineStr">
+      <c r="Z79" t="inlineStr">
         <is>
           <t>a1e053c3-59d7-4967-8041-f699d59f3a5f</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
+      <c r="AA79" t="inlineStr">
         <is>
           <t>778fbbce-86d2-4e74-8f92-f4cc1b9041fe</t>
         </is>
@@ -7467,87 +7513,87 @@
           <t>uf+3+4</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>Earthquale Stomp</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>Earthquale Stomp</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t>-32</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="K80" t="inlineStr">
         <is>
           <t>-32</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr">
+      <c r="N80" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr">
+      <c r="O80" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O80" t="inlineStr">
+      <c r="P80" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="P80" t="inlineStr">
+      <c r="Q80" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="Q80" t="inlineStr">
+      <c r="R80" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="R80" t="inlineStr">
+      <c r="S80" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="S80" t="inlineStr">
+      <c r="T80" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="Y80" t="inlineStr">
+      <c r="Z80" t="inlineStr">
         <is>
           <t>d5733872-becc-4e97-9c6b-eac29a727aa6</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
+      <c r="AA80" t="inlineStr">
         <is>
           <t>b14b5e18-b950-45a2-a10b-f40c73ed239a</t>
         </is>
@@ -7564,52 +7610,52 @@
           <t>3+4</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>Counter Clockwise Spin</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>Counter Clockwise Spin</t>
         </is>
       </c>
-      <c r="O81" t="inlineStr">
+      <c r="P81" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr">
+      <c r="Q81" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q81" t="inlineStr">
+      <c r="R81" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R81" t="inlineStr">
+      <c r="S81" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr">
+      <c r="T81" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W81" t="inlineStr">
+      <c r="X81" t="inlineStr">
         <is>
           <t>Chains into Spinning Razor Kick Variations. First kick will do 20 damage.</t>
         </is>
       </c>
-      <c r="Y81" t="inlineStr">
+      <c r="Z81" t="inlineStr">
         <is>
           <t>cebb8ca0-3f66-439e-9544-66676d7d5e50</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
+      <c r="AA81" t="inlineStr">
         <is>
           <t>14c16edf-1db5-4281-8c87-92c222a904f7</t>
         </is>
@@ -7626,92 +7672,92 @@
           <t>d+4</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>Razor Sweep</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>Razor Sweep</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="K82" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr">
+      <c r="N82" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr">
+      <c r="O82" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="O82" t="inlineStr">
+      <c r="P82" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P82" t="inlineStr">
+      <c r="Q82" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q82" t="inlineStr">
+      <c r="R82" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr">
+      <c r="S82" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="S82" t="inlineStr">
+      <c r="T82" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="V82" t="inlineStr">
+      <c r="W82" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Y82" t="inlineStr">
+      <c r="Z82" t="inlineStr">
         <is>
           <t>c3a15fa4-dd2c-4348-9e5a-4ec064bd9fdd</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
+      <c r="AA82" t="inlineStr">
         <is>
           <t>370befff-d77a-48fc-91bc-2a50407c2aec</t>
         </is>
@@ -7728,87 +7774,87 @@
           <t>d+4,N+4</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>– High Kick</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>Razor Sweep – High Kick</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t>-19</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
+      <c r="K83" t="inlineStr">
         <is>
           <t>-9 -19</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t>-10 -3</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr">
+      <c r="N83" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr">
+      <c r="O83" t="inlineStr">
         <is>
           <t>-10 -3</t>
         </is>
       </c>
-      <c r="O83" t="inlineStr">
+      <c r="P83" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr">
+      <c r="Q83" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="Q83" t="inlineStr">
+      <c r="R83" t="inlineStr">
         <is>
           <t>10,23</t>
         </is>
       </c>
-      <c r="R83" t="inlineStr">
+      <c r="S83" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S83" t="inlineStr">
+      <c r="T83" t="inlineStr">
         <is>
           <t>Lh</t>
         </is>
       </c>
-      <c r="Y83" t="inlineStr">
+      <c r="Z83" t="inlineStr">
         <is>
           <t>456b6584-6a9f-4c98-b6ec-aaeb82608237</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
+      <c r="AA83" t="inlineStr">
         <is>
           <t>164aa7cb-9d5d-4618-b7db-2d28be52f356</t>
         </is>
       </c>
-      <c r="AA83" t="inlineStr">
+      <c r="AB83" t="inlineStr">
         <is>
           <t>c3a15fa4-dd2c-4348-9e5a-4ec064bd9fdd</t>
         </is>
@@ -7825,92 +7871,92 @@
           <t>d+4,d+4</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>– Low Kick</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>Razor Sweep – Low Kick</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
+      <c r="K84" t="inlineStr">
         <is>
           <t>-9 -14</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
+      <c r="L84" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t>-10 -8</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr">
+      <c r="N84" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr">
+      <c r="O84" t="inlineStr">
         <is>
           <t>-10 -8</t>
         </is>
       </c>
-      <c r="O84" t="inlineStr">
+      <c r="P84" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr">
+      <c r="Q84" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q84" t="inlineStr">
+      <c r="R84" t="inlineStr">
         <is>
           <t>10,10</t>
         </is>
       </c>
-      <c r="R84" t="inlineStr">
+      <c r="S84" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="S84" t="inlineStr">
+      <c r="T84" t="inlineStr">
         <is>
           <t>LL</t>
         </is>
       </c>
-      <c r="V84" t="inlineStr">
+      <c r="W84" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Y84" t="inlineStr">
+      <c r="Z84" t="inlineStr">
         <is>
           <t>f2977057-ff04-4ffb-a5ed-9c7fa1cd611b</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
+      <c r="AA84" t="inlineStr">
         <is>
           <t>268ddcd1-4cb0-4444-a840-789f6c364d7a</t>
         </is>
       </c>
-      <c r="AA84" t="inlineStr">
+      <c r="AB84" t="inlineStr">
         <is>
           <t>c3a15fa4-dd2c-4348-9e5a-4ec064bd9fdd</t>
         </is>
@@ -7927,92 +7973,92 @@
           <t>d+4,1</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>– Razor's Edge</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>Razor Sweep – Razor's Edge</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t>-18</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
+      <c r="K85" t="inlineStr">
         <is>
           <t>-9 -18</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
+      <c r="L85" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t>-10 KD</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr">
+      <c r="N85" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr">
+      <c r="O85" t="inlineStr">
         <is>
           <t>-10 KD</t>
         </is>
       </c>
-      <c r="O85" t="inlineStr">
+      <c r="P85" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="P85" t="inlineStr">
+      <c r="Q85" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="Q85" t="inlineStr">
+      <c r="R85" t="inlineStr">
         <is>
           <t>10,21</t>
         </is>
       </c>
-      <c r="R85" t="inlineStr">
+      <c r="S85" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S85" t="inlineStr">
+      <c r="T85" t="inlineStr">
         <is>
           <t>Lm</t>
         </is>
       </c>
-      <c r="V85" t="inlineStr">
+      <c r="W85" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Y85" t="inlineStr">
+      <c r="Z85" t="inlineStr">
         <is>
           <t>c1213fc8-56b7-4005-957c-2a820782fcd9</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
+      <c r="AA85" t="inlineStr">
         <is>
           <t>2a7ec894-86e4-4851-920c-f4b3d645a224</t>
         </is>
       </c>
-      <c r="AA85" t="inlineStr">
+      <c r="AB85" t="inlineStr">
         <is>
           <t>c3a15fa4-dd2c-4348-9e5a-4ec064bd9fdd</t>
         </is>
@@ -8029,92 +8075,92 @@
           <t>4,4</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>Spinning Razor Kicks</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>Spinning Razor Kicks</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="H86" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t>-7 -7</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
+      <c r="K86" t="inlineStr">
         <is>
           <t>-7 -7</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
+      <c r="L86" t="inlineStr">
         <is>
           <t>-7 +4</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
+      <c r="M86" t="inlineStr">
         <is>
           <t>-7 +4</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr">
+      <c r="N86" t="inlineStr">
         <is>
           <t>KD +4</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr">
+      <c r="O86" t="inlineStr">
         <is>
           <t>KD +4</t>
         </is>
       </c>
-      <c r="O86" t="inlineStr">
+      <c r="P86" t="inlineStr">
         <is>
           <t>20,12</t>
         </is>
       </c>
-      <c r="P86" t="inlineStr">
+      <c r="Q86" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="Q86" t="inlineStr">
+      <c r="R86" t="inlineStr">
         <is>
           <t>20,12</t>
         </is>
       </c>
-      <c r="R86" t="inlineStr">
+      <c r="S86" t="inlineStr">
         <is>
           <t>hL</t>
         </is>
       </c>
-      <c r="S86" t="inlineStr">
+      <c r="T86" t="inlineStr">
         <is>
           <t>hL</t>
         </is>
       </c>
-      <c r="V86" t="inlineStr">
+      <c r="W86" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Y86" t="inlineStr">
+      <c r="Z86" t="inlineStr">
         <is>
           <t>d196c117-973c-49f5-b1ae-7b6b1291be92</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
+      <c r="AA86" t="inlineStr">
         <is>
           <t>998dbe9b-429f-4b88-b256-51311008578a</t>
         </is>
@@ -8131,87 +8177,87 @@
           <t>4,4,4</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>– High Kick</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>Spinning Razor Kicks – High Kick</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr">
+      <c r="K87" t="inlineStr">
         <is>
           <t>-7 -7 -14</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
+      <c r="L87" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t>-7 +4 -3</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr">
+      <c r="N87" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr">
+      <c r="O87" t="inlineStr">
         <is>
           <t>KD +4 -3</t>
         </is>
       </c>
-      <c r="O87" t="inlineStr">
+      <c r="P87" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="P87" t="inlineStr">
+      <c r="Q87" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="Q87" t="inlineStr">
+      <c r="R87" t="inlineStr">
         <is>
           <t>20,12,23</t>
         </is>
       </c>
-      <c r="R87" t="inlineStr">
+      <c r="S87" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S87" t="inlineStr">
+      <c r="T87" t="inlineStr">
         <is>
           <t>hLh</t>
         </is>
       </c>
-      <c r="Y87" t="inlineStr">
+      <c r="Z87" t="inlineStr">
         <is>
           <t>df8df186-d787-478b-9067-cc63bd2e4cc1</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
+      <c r="AA87" t="inlineStr">
         <is>
           <t>2cd00b98-f31e-49be-b386-73d9430166c6</t>
         </is>
       </c>
-      <c r="AA87" t="inlineStr">
+      <c r="AB87" t="inlineStr">
         <is>
           <t>d196c117-973c-49f5-b1ae-7b6b1291be92</t>
         </is>
@@ -8228,92 +8274,92 @@
           <t>4,4,d+4</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>– Low Kick</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>Spinning Razor Kicks – Low Kick</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr">
+      <c r="K88" t="inlineStr">
         <is>
           <t>-7 -7 -14</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
+      <c r="L88" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr">
+      <c r="M88" t="inlineStr">
         <is>
           <t>-7 +4 -8</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr">
+      <c r="N88" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr">
+      <c r="O88" t="inlineStr">
         <is>
           <t>KD +4 -8</t>
         </is>
       </c>
-      <c r="O88" t="inlineStr">
+      <c r="P88" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P88" t="inlineStr">
+      <c r="Q88" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q88" t="inlineStr">
+      <c r="R88" t="inlineStr">
         <is>
           <t>20,12,10</t>
         </is>
       </c>
-      <c r="R88" t="inlineStr">
+      <c r="S88" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="S88" t="inlineStr">
+      <c r="T88" t="inlineStr">
         <is>
           <t>hLL</t>
         </is>
       </c>
-      <c r="V88" t="inlineStr">
+      <c r="W88" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Y88" t="inlineStr">
+      <c r="Z88" t="inlineStr">
         <is>
           <t>e8d164c9-8085-4871-aee9-65805ea0fc9d</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
+      <c r="AA88" t="inlineStr">
         <is>
           <t>1f343a2d-8abe-48df-9ded-e864ca580c4b</t>
         </is>
       </c>
-      <c r="AA88" t="inlineStr">
+      <c r="AB88" t="inlineStr">
         <is>
           <t>d196c117-973c-49f5-b1ae-7b6b1291be92</t>
         </is>
@@ -8330,92 +8376,92 @@
           <t>4,4,1</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>– Razor's Edge</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>Spinning Razor Kicks – Razor's Edge</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
+      <c r="J89" t="inlineStr">
         <is>
           <t>-18</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr">
+      <c r="K89" t="inlineStr">
         <is>
           <t>-7 -7 -18</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
+      <c r="L89" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
+      <c r="M89" t="inlineStr">
         <is>
           <t>-7 +4 KD</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr">
+      <c r="N89" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr">
+      <c r="O89" t="inlineStr">
         <is>
           <t>KD +4 KD</t>
         </is>
       </c>
-      <c r="O89" t="inlineStr">
+      <c r="P89" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="P89" t="inlineStr">
+      <c r="Q89" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="Q89" t="inlineStr">
+      <c r="R89" t="inlineStr">
         <is>
           <t>20,12,21</t>
         </is>
       </c>
-      <c r="R89" t="inlineStr">
+      <c r="S89" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S89" t="inlineStr">
+      <c r="T89" t="inlineStr">
         <is>
           <t>hLm</t>
         </is>
       </c>
-      <c r="V89" t="inlineStr">
+      <c r="W89" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Y89" t="inlineStr">
+      <c r="Z89" t="inlineStr">
         <is>
           <t>17d85d26-4edf-4052-acde-e5175b05a043</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
+      <c r="AA89" t="inlineStr">
         <is>
           <t>ed5fe743-7c7d-4be7-882b-f34cf65377eb</t>
         </is>
       </c>
-      <c r="AA89" t="inlineStr">
+      <c r="AB89" t="inlineStr">
         <is>
           <t>d196c117-973c-49f5-b1ae-7b6b1291be92</t>
         </is>
@@ -8432,92 +8478,92 @@
           <t>WS+4</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>Skyscraper Kick</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>Skyscraper Kick</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="H90" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr">
+      <c r="K90" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
+      <c r="L90" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr">
+      <c r="N90" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr">
+      <c r="O90" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O90" t="inlineStr">
+      <c r="P90" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P90" t="inlineStr">
+      <c r="Q90" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q90" t="inlineStr">
+      <c r="R90" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R90" t="inlineStr">
+      <c r="S90" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S90" t="inlineStr">
+      <c r="T90" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V90" t="inlineStr">
+      <c r="W90" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Y90" t="inlineStr">
+      <c r="Z90" t="inlineStr">
         <is>
           <t>59b33e5c-2c1c-4221-97df-7f4aa99bce1d</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
+      <c r="AA90" t="inlineStr">
         <is>
           <t>3d4ec81e-e6f6-4b08-8f41-223aae8ee591</t>
         </is>
@@ -8534,87 +8580,87 @@
           <t>FC+df+4,3</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>Bow &amp; Arrow</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>Bow &amp; Arrow</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="H91" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t>-14 -14</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr">
+      <c r="K91" t="inlineStr">
         <is>
           <t>-14 -14</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
+      <c r="L91" t="inlineStr">
         <is>
           <t>-3 KD</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
+      <c r="M91" t="inlineStr">
         <is>
           <t>-3 KD</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr">
+      <c r="N91" t="inlineStr">
         <is>
           <t>-3 KD</t>
         </is>
       </c>
-      <c r="N91" t="inlineStr">
+      <c r="O91" t="inlineStr">
         <is>
           <t>-3 KD</t>
         </is>
       </c>
-      <c r="O91" t="inlineStr">
+      <c r="P91" t="inlineStr">
         <is>
           <t>12,15</t>
         </is>
       </c>
-      <c r="P91" t="inlineStr">
+      <c r="Q91" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="Q91" t="inlineStr">
+      <c r="R91" t="inlineStr">
         <is>
           <t>12,15</t>
         </is>
       </c>
-      <c r="R91" t="inlineStr">
+      <c r="S91" t="inlineStr">
         <is>
           <t>Lm</t>
         </is>
       </c>
-      <c r="S91" t="inlineStr">
+      <c r="T91" t="inlineStr">
         <is>
           <t>Lm</t>
         </is>
       </c>
-      <c r="Y91" t="inlineStr">
+      <c r="Z91" t="inlineStr">
         <is>
           <t>e122f2ea-169b-4209-9c0a-3fdc5ba27030</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
+      <c r="AA91" t="inlineStr">
         <is>
           <t>a51c4903-f0fc-4c0a-b761-336f399118d3</t>
         </is>
@@ -8631,47 +8677,47 @@
           <t>u,ub</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="E92" t="inlineStr">
         <is>
           <t>Evasive Backflip</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>Evasive Backflip</t>
         </is>
       </c>
-      <c r="O92" t="inlineStr">
+      <c r="P92" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P92" t="inlineStr">
+      <c r="Q92" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q92" t="inlineStr">
+      <c r="R92" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R92" t="inlineStr">
+      <c r="S92" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S92" t="inlineStr">
+      <c r="T92" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y92" t="inlineStr">
+      <c r="Z92" t="inlineStr">
         <is>
           <t>152ffaa4-a0f7-47ae-a198-d60c80d100ff</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
+      <c r="AA92" t="inlineStr">
         <is>
           <t>f241dac6-4c7b-4eda-ae31-19e5ee8e0676</t>
         </is>
@@ -8703,125 +8749,130 @@
       </c>
       <c r="D95" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="E95" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="E95" s="1" t="inlineStr">
+      <c r="F95" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="F95" s="1" t="inlineStr">
+      <c r="G95" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="G95" s="1" t="inlineStr">
+      <c r="H95" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="H95" s="1" t="inlineStr">
+      <c r="I95" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="I95" s="1" t="inlineStr">
+      <c r="J95" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="J95" s="1" t="inlineStr">
+      <c r="K95" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="K95" s="1" t="inlineStr">
+      <c r="L95" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="L95" s="1" t="inlineStr">
+      <c r="M95" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="M95" s="1" t="inlineStr">
+      <c r="N95" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="N95" s="1" t="inlineStr">
+      <c r="O95" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="O95" s="1" t="inlineStr">
+      <c r="P95" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="P95" s="1" t="inlineStr">
+      <c r="Q95" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="Q95" s="1" t="inlineStr">
+      <c r="R95" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="R95" s="1" t="inlineStr">
+      <c r="S95" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="S95" s="1" t="inlineStr">
+      <c r="T95" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="T95" s="1" t="inlineStr">
+      <c r="U95" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="U95" s="1" t="inlineStr">
+      <c r="V95" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="V95" s="1" t="inlineStr">
+      <c r="W95" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="W95" s="1" t="inlineStr">
+      <c r="X95" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="X95" s="1" t="inlineStr">
+      <c r="Y95" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Y95" s="1" t="inlineStr">
+      <c r="Z95" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Z95" s="1" t="inlineStr">
+      <c r="AA95" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AA95" s="1" t="inlineStr">
+      <c r="AB95" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AB95" s="1" t="inlineStr">
+      <c r="AC95" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -8838,82 +8889,82 @@
           <t>f+1+4</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="E96" t="inlineStr">
         <is>
           <t>Heaven Cannon</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="F96" t="inlineStr">
         <is>
           <t>Heaven Cannon</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="H96" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="I96" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
+      <c r="L96" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr">
+      <c r="M96" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M96" t="inlineStr">
+      <c r="N96" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N96" t="inlineStr">
+      <c r="O96" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O96" t="inlineStr">
+      <c r="P96" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="P96" t="inlineStr">
+      <c r="Q96" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="Q96" t="inlineStr">
+      <c r="R96" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="R96" t="inlineStr">
+      <c r="S96" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="S96" t="inlineStr">
+      <c r="T96" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="V96" t="inlineStr">
+      <c r="W96" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Y96" t="inlineStr">
+      <c r="Z96" t="inlineStr">
         <is>
           <t>b9ded0c3-ba9c-4d6d-b4ca-8e483fb268ff</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
+      <c r="AA96" t="inlineStr">
         <is>
           <t>6cfcb003-d712-4ca7-b995-aebc0458c502</t>
         </is>
@@ -8945,125 +8996,130 @@
       </c>
       <c r="D99" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="E99" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="E99" s="1" t="inlineStr">
+      <c r="F99" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="F99" s="1" t="inlineStr">
+      <c r="G99" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="G99" s="1" t="inlineStr">
+      <c r="H99" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="H99" s="1" t="inlineStr">
+      <c r="I99" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="I99" s="1" t="inlineStr">
+      <c r="J99" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="J99" s="1" t="inlineStr">
+      <c r="K99" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="K99" s="1" t="inlineStr">
+      <c r="L99" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="L99" s="1" t="inlineStr">
+      <c r="M99" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="M99" s="1" t="inlineStr">
+      <c r="N99" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="N99" s="1" t="inlineStr">
+      <c r="O99" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="O99" s="1" t="inlineStr">
+      <c r="P99" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="P99" s="1" t="inlineStr">
+      <c r="Q99" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="Q99" s="1" t="inlineStr">
+      <c r="R99" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="R99" s="1" t="inlineStr">
+      <c r="S99" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="S99" s="1" t="inlineStr">
+      <c r="T99" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="T99" s="1" t="inlineStr">
+      <c r="U99" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="U99" s="1" t="inlineStr">
+      <c r="V99" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="V99" s="1" t="inlineStr">
+      <c r="W99" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="W99" s="1" t="inlineStr">
+      <c r="X99" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="X99" s="1" t="inlineStr">
+      <c r="Y99" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Y99" s="1" t="inlineStr">
+      <c r="Z99" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Z99" s="1" t="inlineStr">
+      <c r="AA99" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AA99" s="1" t="inlineStr">
+      <c r="AB99" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AB99" s="1" t="inlineStr">
+      <c r="AC99" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -9080,42 +9136,42 @@
           <t>2,1,1,2,3,3,3,4,4,1</t>
         </is>
       </c>
-      <c r="O100" t="inlineStr">
+      <c r="P100" t="inlineStr">
         <is>
           <t>8,6,6,6,6,6,6,7,8,25</t>
         </is>
       </c>
-      <c r="P100" t="inlineStr">
+      <c r="Q100" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="Q100" t="inlineStr">
+      <c r="R100" t="inlineStr">
         <is>
           <t>8,6,6,6,6,6,6,7,8,25</t>
         </is>
       </c>
-      <c r="R100" t="inlineStr">
+      <c r="S100" t="inlineStr">
         <is>
           <t>hmmhLmhhLm</t>
         </is>
       </c>
-      <c r="S100" t="inlineStr">
+      <c r="T100" t="inlineStr">
         <is>
           <t>hmmhLmhhLm</t>
         </is>
       </c>
-      <c r="Y100" t="inlineStr">
+      <c r="Z100" t="inlineStr">
         <is>
           <t>0fc0ca0b-d962-4684-9515-834d1e1283b6</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
+      <c r="AA100" t="inlineStr">
         <is>
           <t>0fc0ca0b-d962-4684-9515-834d1e1283b6</t>
         </is>
       </c>
-      <c r="AB100" t="inlineStr">
+      <c r="AC100" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -9132,42 +9188,42 @@
           <t>2,1,1,2,3,3,2,3,2,1</t>
         </is>
       </c>
-      <c r="O101" t="inlineStr">
+      <c r="P101" t="inlineStr">
         <is>
           <t>8,6,6,6,6,6,7,5,5,30</t>
         </is>
       </c>
-      <c r="P101" t="inlineStr">
+      <c r="Q101" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="Q101" t="inlineStr">
+      <c r="R101" t="inlineStr">
         <is>
           <t>8,6,6,6,6,6,7,5,5,30</t>
         </is>
       </c>
-      <c r="R101" t="inlineStr">
+      <c r="S101" t="inlineStr">
         <is>
           <t>hmmhLmmLm!</t>
         </is>
       </c>
-      <c r="S101" t="inlineStr">
+      <c r="T101" t="inlineStr">
         <is>
           <t>hmmhLmmLm!</t>
         </is>
       </c>
-      <c r="Y101" t="inlineStr">
+      <c r="Z101" t="inlineStr">
         <is>
           <t>b5de5a0d-851a-4ca2-ad04-246afb578ddb</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
+      <c r="AA101" t="inlineStr">
         <is>
           <t>b5de5a0d-851a-4ca2-ad04-246afb578ddb</t>
         </is>
       </c>
-      <c r="AB101" t="inlineStr">
+      <c r="AC101" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -9184,42 +9240,42 @@
           <t>2,1,1,2,3,3,2,1,4,3</t>
         </is>
       </c>
-      <c r="O102" t="inlineStr">
+      <c r="P102" t="inlineStr">
         <is>
           <t>8,6,6,6,6,67,7,10,25</t>
         </is>
       </c>
-      <c r="P102" t="inlineStr">
+      <c r="Q102" t="inlineStr">
         <is>
           <t>141</t>
         </is>
       </c>
-      <c r="Q102" t="inlineStr">
+      <c r="R102" t="inlineStr">
         <is>
           <t>8,6,6,6,6,67,7,10,25</t>
         </is>
       </c>
-      <c r="R102" t="inlineStr">
+      <c r="S102" t="inlineStr">
         <is>
           <t>hmmhLmmmLm</t>
         </is>
       </c>
-      <c r="S102" t="inlineStr">
+      <c r="T102" t="inlineStr">
         <is>
           <t>hmmhLmmmLm</t>
         </is>
       </c>
-      <c r="Y102" t="inlineStr">
+      <c r="Z102" t="inlineStr">
         <is>
           <t>04575a0d-bb87-4254-a98a-681589f81afc</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
+      <c r="AA102" t="inlineStr">
         <is>
           <t>04575a0d-bb87-4254-a98a-681589f81afc</t>
         </is>
       </c>
-      <c r="AB102" t="inlineStr">
+      <c r="AC102" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
